--- a/data/trans_bre/IP18A05-Estudios-trans_bre.xlsx
+++ b/data/trans_bre/IP18A05-Estudios-trans_bre.xlsx
@@ -660,22 +660,22 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-6,97; 0,0</t>
+          <t>-7,96; 0,0</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-2,99; 1,54</t>
+          <t>-3,88; 1,53</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,57</t>
+          <t>0,0; 8,08</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-56,4; 0,0</t>
+          <t>-57,26; 0,0</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -760,37 +760,37 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-0,3; 1,48</t>
+          <t>-0,34; 1,43</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-0,49; 1,39</t>
+          <t>-0,58; 1,45</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-2,22; 0,7</t>
+          <t>-2,1; 0,73</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-7,39; 1,94</t>
+          <t>-7,79; 1,98</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-100,0; —</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-67,75; 643,72</t>
+          <t>-72,08; 662,96</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-79,3; 86,17</t>
+          <t>-79,95; 78,06</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -860,22 +860,22 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-0,69; 2,22</t>
+          <t>-0,69; 2,01</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-4,68; -0,17</t>
+          <t>-4,6; -0,21</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-1,67; 1,52</t>
+          <t>-1,82; 1,49</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>1,51; 15,48</t>
+          <t>1,51; 17,14</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -885,7 +885,7 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 136,92</t>
+          <t>-100,0; —</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-0,63; 0,83</t>
+          <t>-0,72; 0,86</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-1,18; 0,59</t>
+          <t>-1,11; 0,61</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-1,32; 0,87</t>
+          <t>-1,32; 0,81</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-6,51; 2,44</t>
+          <t>-6,24; 2,35</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-77,28; 418,65</t>
+          <t>-80,53; 408,35</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-73,94; 98,78</t>
+          <t>-74,08; 111,3</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-65,93; 126,33</t>
+          <t>-67,66; 105,86</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-89,06; 125,86</t>
+          <t>-90,42; 142,83</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/IP18A05-Estudios-trans_bre.xlsx
+++ b/data/trans_bre/IP18A05-Estudios-trans_bre.xlsx
@@ -660,22 +660,22 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-7,96; 0,0</t>
+          <t>-8,12; 0,0</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-3,88; 1,53</t>
+          <t>-3,39; 1,53</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 8,08</t>
+          <t>0,0; 8,02</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-57,26; 0,0</t>
+          <t>-55,31; 0,0</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -760,37 +760,37 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-0,34; 1,43</t>
+          <t>-0,29; 1,55</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-0,58; 1,45</t>
+          <t>-0,62; 1,35</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-2,1; 0,73</t>
+          <t>-2,27; 0,72</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-7,79; 1,98</t>
+          <t>-7,75; 2,43</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-100,0; —</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-72,08; 662,96</t>
+          <t>-72,24; 647,11</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-79,95; 78,06</t>
+          <t>-80,3; 99,58</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -860,22 +860,22 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-0,69; 2,01</t>
+          <t>-0,69; 2,06</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-4,6; -0,21</t>
+          <t>-4,82; -0,31</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-1,82; 1,49</t>
+          <t>-1,78; 1,22</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>1,51; 17,14</t>
+          <t>1,43; 15,32</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -885,7 +885,7 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-100,0; —</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-0,72; 0,86</t>
+          <t>-0,73; 0,77</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-1,11; 0,61</t>
+          <t>-1,17; 0,65</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-1,32; 0,81</t>
+          <t>-1,31; 0,66</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-6,24; 2,35</t>
+          <t>-6,08; 2,5</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-80,53; 408,35</t>
+          <t>-79,44; 334,34</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-74,08; 111,3</t>
+          <t>-74,15; 116,48</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-67,66; 105,86</t>
+          <t>-68,33; 82,77</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-90,42; 142,83</t>
+          <t>-85,87; 135,36</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/IP18A05-Estudios-trans_bre.xlsx
+++ b/data/trans_bre/IP18A05-Estudios-trans_bre.xlsx
@@ -522,7 +522,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que su última consulta al médico fue por dispensación de recetas</t>
+          <t>Menores cuya última consulta médica fue por dispensación de recetas</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -627,7 +627,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>-20,36</t>
+          <t>-21,03</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -660,22 +660,22 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-8,12; 0,0</t>
+          <t>-6,97; 0,0</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-3,39; 1,53</t>
+          <t>-2,99; 1,54</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 8,02</t>
+          <t>0,0; 7,57</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-55,31; 0,0</t>
+          <t>-58,06; 0,0</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -727,7 +727,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>-2,15</t>
+          <t>-2,18</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>-51,79%</t>
+          <t>-50,74%</t>
         </is>
       </c>
     </row>
@@ -760,22 +760,22 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-0,29; 1,55</t>
+          <t>-0,3; 1,48</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-0,62; 1,35</t>
+          <t>-0,49; 1,39</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-2,27; 0,72</t>
+          <t>-2,22; 0,7</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-7,75; 2,43</t>
+          <t>-7,89; 2,1</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -785,12 +785,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-72,24; 647,11</t>
+          <t>-67,75; 643,72</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-80,3; 99,58</t>
+          <t>-79,3; 86,17</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -827,7 +827,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>5,7</t>
+          <t>5,34</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -860,22 +860,22 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-0,69; 2,06</t>
+          <t>-0,69; 2,22</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-4,82; -0,31</t>
+          <t>-4,68; -0,17</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-1,78; 1,22</t>
+          <t>-1,67; 1,52</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>1,43; 15,32</t>
+          <t>1,35; 14,71</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -885,7 +885,7 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-100,0; 136,92</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
@@ -927,7 +927,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>-1,46</t>
+          <t>-1,66</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>-33,54%</t>
+          <t>-36,59%</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-0,73; 0,77</t>
+          <t>-0,63; 0,83</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-1,17; 0,65</t>
+          <t>-1,18; 0,59</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-1,31; 0,66</t>
+          <t>-1,32; 0,87</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-6,08; 2,5</t>
+          <t>-7,05; 2,41</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-79,44; 334,34</t>
+          <t>-77,28; 418,65</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-74,15; 116,48</t>
+          <t>-73,94; 98,78</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-68,33; 82,77</t>
+          <t>-65,93; 126,33</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-85,87; 135,36</t>
+          <t>-90,42; 127,21</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/IP18A05-Estudios-trans_bre.xlsx
+++ b/data/trans_bre/IP18A05-Estudios-trans_bre.xlsx
@@ -16,7 +16,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="2">
+    <numFmt numFmtId="164" formatCode="0.##"/>
+    <numFmt numFmtId="165" formatCode="0.##%"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <name val="Calibri"/>
@@ -125,7 +128,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -138,6 +141,12 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -504,7 +513,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J12"/>
+  <dimension ref="A1:J16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -610,299 +619,177 @@
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>-2,24</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>-0,2</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>2,23</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>-21,03</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>-100,0%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>-20,68%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>inf%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>-100,0%</t>
-        </is>
+      <c r="C4" s="5" t="n">
+        <v>-2.243761250252916</v>
+      </c>
+      <c r="D4" s="5" t="n">
+        <v>-0.1988139043013473</v>
+      </c>
+      <c r="E4" s="5" t="n">
+        <v>2.234148749587908</v>
+      </c>
+      <c r="F4" s="5" t="n">
+        <v>-21.03224376645586</v>
+      </c>
+      <c r="G4" s="6" t="n">
+        <v>-1</v>
+      </c>
+      <c r="H4" s="6" t="n">
+        <v>-0.2067550131568529</v>
+      </c>
+      <c r="I4" s="6" t="inlineStr">
+        <is>
+          <t>inf</t>
+        </is>
+      </c>
+      <c r="J4" s="6" t="n">
+        <v>-1</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n"/>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>-6,97; 0,0</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>-2,99; 1,54</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 7,57</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>-58,06; 0,0</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="n">
+        <v>-6.969202253404062</v>
+      </c>
+      <c r="D5" s="5" t="n">
+        <v>-2.98736365707421</v>
+      </c>
+      <c r="E5" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F5" s="5" t="n">
+        <v>-58.05858139528326</v>
+      </c>
+      <c r="G5" s="6" t="inlineStr"/>
+      <c r="H5" s="6" t="inlineStr"/>
+      <c r="I5" s="6" t="inlineStr"/>
+      <c r="J5" s="6" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="inlineStr">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D6" s="5" t="n">
+        <v>1.540040594714853</v>
+      </c>
+      <c r="E6" s="5" t="n">
+        <v>7.570599912385364</v>
+      </c>
+      <c r="F6" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G6" s="6" t="inlineStr"/>
+      <c r="H6" s="6" t="inlineStr"/>
+      <c r="I6" s="6" t="inlineStr"/>
+      <c r="J6" s="6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
         <is>
           <t>Secundarios</t>
         </is>
       </c>
-      <c r="B6" s="3" t="inlineStr">
+      <c r="B7" s="3" t="inlineStr">
         <is>
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>0,44</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>0,36</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>-0,69</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>-2,18</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>131,9%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>57,64%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>-37,34%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>-50,74%</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="1" t="n"/>
-      <c r="B7" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>-0,3; 1,48</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>-0,49; 1,39</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>-2,22; 0,7</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>-7,89; 2,1</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>-67,75; 643,72</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>-79,3; 86,17</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
+      <c r="C7" s="5" t="n">
+        <v>0.444645857458221</v>
+      </c>
+      <c r="D7" s="5" t="n">
+        <v>0.3611867132768011</v>
+      </c>
+      <c r="E7" s="5" t="n">
+        <v>-0.6897004982960725</v>
+      </c>
+      <c r="F7" s="5" t="n">
+        <v>-2.180329009197948</v>
+      </c>
+      <c r="G7" s="6" t="n">
+        <v>1.319016458111593</v>
+      </c>
+      <c r="H7" s="6" t="n">
+        <v>0.5763516506662162</v>
+      </c>
+      <c r="I7" s="6" t="n">
+        <v>-0.3734063529619524</v>
+      </c>
+      <c r="J7" s="6" t="n">
+        <v>-0.5074210411500615</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>Universitarios</t>
-        </is>
-      </c>
+      <c r="A8" s="1" t="n"/>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>0,17</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>-2,08</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>-0,08</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>5,34</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>48,78%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>-80,42%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>-9,14%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>inf%</t>
-        </is>
-      </c>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="n">
+        <v>-0.295235397168383</v>
+      </c>
+      <c r="D8" s="5" t="n">
+        <v>-0.4885449179015114</v>
+      </c>
+      <c r="E8" s="5" t="n">
+        <v>-2.216994021570812</v>
+      </c>
+      <c r="F8" s="5" t="n">
+        <v>-7.89080605306056</v>
+      </c>
+      <c r="G8" s="6" t="inlineStr"/>
+      <c r="H8" s="6" t="n">
+        <v>-0.6775188903662089</v>
+      </c>
+      <c r="I8" s="6" t="n">
+        <v>-0.7929622513463943</v>
+      </c>
+      <c r="J8" s="6" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n"/>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>-0,69; 2,22</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>-4,68; -0,17</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>-1,67; 1,52</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>1,35; 14,71</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>-100,0; 136,92</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="n">
+        <v>1.483178182495428</v>
+      </c>
+      <c r="D9" s="5" t="n">
+        <v>1.393916161031094</v>
+      </c>
+      <c r="E9" s="5" t="n">
+        <v>0.7033411618738147</v>
+      </c>
+      <c r="F9" s="5" t="n">
+        <v>2.10243317614647</v>
+      </c>
+      <c r="G9" s="6" t="inlineStr"/>
+      <c r="H9" s="6" t="n">
+        <v>6.437221168806698</v>
+      </c>
+      <c r="I9" s="6" t="n">
+        <v>0.8617288343587249</v>
+      </c>
+      <c r="J9" s="6" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>Universitarios</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
@@ -910,44 +797,30 @@
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>0,05</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>-0,27</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>-0,26</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>-1,66</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>9,64%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>-24,19%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>-18,5%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>-36,59%</t>
+      <c r="C10" s="5" t="n">
+        <v>0.1684731682947981</v>
+      </c>
+      <c r="D10" s="5" t="n">
+        <v>-2.080022626739011</v>
+      </c>
+      <c r="E10" s="5" t="n">
+        <v>-0.07838465416407492</v>
+      </c>
+      <c r="F10" s="5" t="n">
+        <v>5.335357839737717</v>
+      </c>
+      <c r="G10" s="6" t="n">
+        <v>0.4877614278262128</v>
+      </c>
+      <c r="H10" s="6" t="n">
+        <v>-0.804207692013255</v>
+      </c>
+      <c r="I10" s="6" t="n">
+        <v>-0.09140702363835905</v>
+      </c>
+      <c r="J10" s="6" t="inlineStr">
+        <is>
+          <t>inf</t>
         </is>
       </c>
     </row>
@@ -955,52 +828,156 @@
       <c r="A11" s="1" t="n"/>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>-0,63; 0,83</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>-1,18; 0,59</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>-1,32; 0,87</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>-7,05; 2,41</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>-77,28; 418,65</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>-73,94; 98,78</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>-65,93; 126,33</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>-90,42; 127,21</t>
-        </is>
-      </c>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="n">
+        <v>-0.6909146898748605</v>
+      </c>
+      <c r="D11" s="5" t="n">
+        <v>-4.683046887312361</v>
+      </c>
+      <c r="E11" s="5" t="n">
+        <v>-1.666564104114855</v>
+      </c>
+      <c r="F11" s="5" t="n">
+        <v>1.345127766273728</v>
+      </c>
+      <c r="G11" s="6" t="inlineStr"/>
+      <c r="H11" s="6" t="n">
+        <v>-1</v>
+      </c>
+      <c r="I11" s="6" t="inlineStr"/>
+      <c r="J11" s="6" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" t="inlineStr">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="n">
+        <v>2.215658314600079</v>
+      </c>
+      <c r="D12" s="5" t="n">
+        <v>-0.1657644158010829</v>
+      </c>
+      <c r="E12" s="5" t="n">
+        <v>1.524984325959008</v>
+      </c>
+      <c r="F12" s="5" t="n">
+        <v>14.71134248395936</v>
+      </c>
+      <c r="G12" s="6" t="inlineStr"/>
+      <c r="H12" s="6" t="n">
+        <v>1.369192101443654</v>
+      </c>
+      <c r="I12" s="6" t="inlineStr"/>
+      <c r="J12" s="6" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="n">
+        <v>0.05453311838271736</v>
+      </c>
+      <c r="D13" s="5" t="n">
+        <v>-0.2697351010002872</v>
+      </c>
+      <c r="E13" s="5" t="n">
+        <v>-0.2630966996693263</v>
+      </c>
+      <c r="F13" s="5" t="n">
+        <v>-1.657317290887217</v>
+      </c>
+      <c r="G13" s="6" t="n">
+        <v>0.09643244564111202</v>
+      </c>
+      <c r="H13" s="6" t="n">
+        <v>-0.2418644776486493</v>
+      </c>
+      <c r="I13" s="6" t="n">
+        <v>-0.1849929003580277</v>
+      </c>
+      <c r="J13" s="6" t="n">
+        <v>-0.3659091201664524</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="n">
+        <v>-0.6346958310687388</v>
+      </c>
+      <c r="D14" s="5" t="n">
+        <v>-1.182199887670607</v>
+      </c>
+      <c r="E14" s="5" t="n">
+        <v>-1.317886393158057</v>
+      </c>
+      <c r="F14" s="5" t="n">
+        <v>-7.051049880257816</v>
+      </c>
+      <c r="G14" s="6" t="n">
+        <v>-0.7728323084210057</v>
+      </c>
+      <c r="H14" s="6" t="n">
+        <v>-0.739355817583554</v>
+      </c>
+      <c r="I14" s="6" t="n">
+        <v>-0.6593208707567378</v>
+      </c>
+      <c r="J14" s="6" t="n">
+        <v>-0.9041606243637619</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="n">
+        <v>0.826484318947885</v>
+      </c>
+      <c r="D15" s="5" t="n">
+        <v>0.5856293399350855</v>
+      </c>
+      <c r="E15" s="5" t="n">
+        <v>0.8732050977106874</v>
+      </c>
+      <c r="F15" s="5" t="n">
+        <v>2.413484040426134</v>
+      </c>
+      <c r="G15" s="6" t="n">
+        <v>4.186538061191979</v>
+      </c>
+      <c r="H15" s="6" t="n">
+        <v>0.9877997684589129</v>
+      </c>
+      <c r="I15" s="6" t="n">
+        <v>1.263341045380128</v>
+      </c>
+      <c r="J15" s="6" t="n">
+        <v>1.272075345212049</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
         <is>
           <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
         </is>
@@ -1008,13 +985,13 @@
     </row>
   </sheetData>
   <mergeCells count="7">
-    <mergeCell ref="A8:A9"/>
-    <mergeCell ref="A4:A5"/>
-    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A10:A12"/>
     <mergeCell ref="C1:F1"/>
     <mergeCell ref="G1:J1"/>
-    <mergeCell ref="A6:A7"/>
-    <mergeCell ref="A10:A11"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="A13:A15"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
